--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.77990371225928</v>
+        <v>6.789234353242133</v>
       </c>
       <c r="D2" t="n">
-        <v>41.86595789156153</v>
+        <v>6.803218157378748</v>
       </c>
       <c r="E2" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F2" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.84580693369634</v>
+        <v>4.524943626725656</v>
       </c>
       <c r="D3" t="n">
-        <v>27.81738395098725</v>
+        <v>4.520324892035427</v>
       </c>
       <c r="E3" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F3" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.06086821332151</v>
+        <v>5.859891084664746</v>
       </c>
       <c r="D4" t="n">
-        <v>37.55857730213511</v>
+        <v>6.103268811596955</v>
       </c>
       <c r="E4" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F4" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.53429486829117</v>
+        <v>1.711822916097316</v>
       </c>
       <c r="D5" t="n">
-        <v>16.28828630241407</v>
+        <v>2.646846524142286</v>
       </c>
       <c r="E5" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F5" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.84971836180909</v>
+        <v>5.988079233793977</v>
       </c>
       <c r="D6" t="n">
-        <v>36.59033910657865</v>
+        <v>5.945930104819031</v>
       </c>
       <c r="E6" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F6" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.72297227024587</v>
+        <v>5.317482993914954</v>
       </c>
       <c r="D7" t="n">
-        <v>32.76503376295233</v>
+        <v>5.324317986479755</v>
       </c>
       <c r="E7" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F7" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.1481705147453</v>
+        <v>1.811577708646111</v>
       </c>
       <c r="D8" t="n">
-        <v>11.72956450053945</v>
+        <v>1.90605423133766</v>
       </c>
       <c r="E8" t="n">
-        <v>11.61538030944339</v>
+        <v>1.887499300284551</v>
       </c>
       <c r="F8" t="n">
-        <v>10.49797506738884</v>
+        <v>1.705920948450687</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
